--- a/result.xlsx
+++ b/result.xlsx
@@ -566,31 +566,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:X102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="7" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -628,117 +630,127 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>Father Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>DOB</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Roll
 No.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Hindi
 (FM)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Hindi
 (Obt)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>English
 (FM)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>English
 (Obt)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Math
 (FM)</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Math
 (Obt)</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>EVS
 (FM)</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>EVS
 (Obt)</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Science
 (FM)</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Science
 (Obt)</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Soc.Sci
 (FM)</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Soc.Sci
 (Obt)</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Sanskrit
 (FM)</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>Sanskrit
 (Obt)</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>Full
 Marks</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>Total
 Obt.</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -762,52 +774,62 @@
           <t>Kajali Kumari</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Devendra Tiwari</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>26-Nov-2018</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n"/>
       <c r="O6" s="6" t="n"/>
       <c r="P6" s="6" t="n"/>
       <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="U6" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="T6" s="6" t="inlineStr">
+      <c r="V6" s="6" t="inlineStr">
         <is>
           <t>68.00%</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V6" s="9" t="inlineStr">
+      <c r="X6" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -824,52 +846,62 @@
           <t>Anushka Kumari</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Shambhu Tanti</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>03-Aug-2018</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="F7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" s="10" t="n">
+      <c r="H7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="10" t="n">
+      <c r="J7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
       <c r="Q7" s="10" t="n"/>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="S7" s="10" t="n">
+      <c r="U7" s="10" t="n">
         <v>131</v>
       </c>
-      <c r="T7" s="10" t="inlineStr">
+      <c r="V7" s="10" t="inlineStr">
         <is>
           <t>87.33%</t>
         </is>
       </c>
-      <c r="U7" s="12" t="inlineStr">
+      <c r="W7" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V7" s="12" t="inlineStr">
+      <c r="X7" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -886,14 +918,18 @@
           <t>Anushka Kumari</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Kanhaiya Modi</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>05-Feb-2018</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>40</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>50</v>
@@ -905,33 +941,39 @@
         <v>50</v>
       </c>
       <c r="I8" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
       <c r="O8" s="6" t="n"/>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n">
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="U8" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="T8" s="6" t="inlineStr">
+      <c r="V8" s="6" t="inlineStr">
         <is>
           <t>84.00%</t>
         </is>
       </c>
-      <c r="U8" s="9" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V8" s="9" t="inlineStr">
+      <c r="X8" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -948,52 +990,62 @@
           <t>Chandani Kumari</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Niraj Singh</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>07-Dec-2019</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="10" t="n">
+      <c r="F9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" s="10" t="n">
+      <c r="H9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I9" s="10" t="n">
+      <c r="J9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
       <c r="Q9" s="10" t="n"/>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="S9" s="10" t="n">
+      <c r="U9" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="T9" s="10" t="inlineStr">
+      <c r="V9" s="10" t="inlineStr">
         <is>
           <t>80.67%</t>
         </is>
       </c>
-      <c r="U9" s="13" t="inlineStr">
+      <c r="W9" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V9" s="12" t="inlineStr">
+      <c r="X9" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1010,14 +1062,18 @@
           <t>Sunny Kumar</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Pintu Kumar</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>01-Jan-2019</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>25</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>50</v>
@@ -1029,33 +1085,39 @@
         <v>50</v>
       </c>
       <c r="I10" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="n">
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n"/>
+      <c r="T10" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="U10" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="V10" s="6" t="inlineStr">
         <is>
           <t>54.67%</t>
         </is>
       </c>
-      <c r="U10" s="14" t="inlineStr">
+      <c r="W10" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V10" s="9" t="inlineStr">
+      <c r="X10" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1072,20 +1134,24 @@
           <t>Tanmay Kumar</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar Tiwari</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>05-Jan-2019</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" s="10" t="n">
+      <c r="F11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>25</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>28</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>50</v>
@@ -1093,31 +1159,37 @@
       <c r="I11" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="10" t="n"/>
+      <c r="J11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>28</v>
+      </c>
       <c r="L11" s="10" t="n"/>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
       <c r="P11" s="10" t="n"/>
       <c r="Q11" s="10" t="n"/>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="S11" s="10" t="n">
+      <c r="U11" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="T11" s="10" t="inlineStr">
+      <c r="V11" s="10" t="inlineStr">
         <is>
           <t>54.00%</t>
         </is>
       </c>
-      <c r="U11" s="15" t="inlineStr">
+      <c r="W11" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V11" s="12" t="inlineStr">
+      <c r="X11" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1134,52 +1206,62 @@
           <t>Satyam Kumar</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Pintu Kumar</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>03-Jun-2020</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I12" s="6" t="n">
+      <c r="J12" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
+      <c r="T12" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="U12" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="T12" s="6" t="inlineStr">
+      <c r="V12" s="6" t="inlineStr">
         <is>
           <t>50.67%</t>
         </is>
       </c>
-      <c r="U12" s="14" t="inlineStr">
+      <c r="W12" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V12" s="9" t="inlineStr">
+      <c r="X12" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1208,6 +1290,8 @@
       <c r="T13" s="16" t="n"/>
       <c r="U13" s="16" t="n"/>
       <c r="V13" s="16" t="n"/>
+      <c r="W13" s="16" t="n"/>
+      <c r="X13" s="16" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1227,14 +1311,18 @@
           <t>Shivam Kumar</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Manohar Tanti</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>04-Mar-2017</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>45</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>50</v>
@@ -1248,31 +1336,37 @@
       <c r="I15" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
+      <c r="T15" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="U15" s="6" t="n">
         <v>135</v>
       </c>
-      <c r="T15" s="6" t="inlineStr">
+      <c r="V15" s="6" t="inlineStr">
         <is>
           <t>90.00%</t>
         </is>
       </c>
-      <c r="U15" s="9" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V15" s="9" t="inlineStr">
+      <c r="X15" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1289,52 +1383,62 @@
           <t>Anmol Kumar</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Onkar Kumar Das</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>12-Nov-2017</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="F16" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G16" s="10" t="n">
+      <c r="H16" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="H16" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" s="10" t="n">
+      <c r="J16" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K16" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
       <c r="L16" s="10" t="n"/>
       <c r="M16" s="10" t="n"/>
       <c r="N16" s="10" t="n"/>
       <c r="O16" s="10" t="n"/>
       <c r="P16" s="10" t="n"/>
       <c r="Q16" s="10" t="n"/>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="S16" s="10" t="n">
+      <c r="U16" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="T16" s="10" t="inlineStr">
+      <c r="V16" s="10" t="inlineStr">
         <is>
           <t>67.33%</t>
         </is>
       </c>
-      <c r="U16" s="13" t="inlineStr">
+      <c r="W16" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V16" s="12" t="inlineStr">
+      <c r="X16" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1351,14 +1455,18 @@
           <t>Raj Pritam Kumar</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Babalu Tanti</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>11-Aug-2018</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>35</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>50</v>
@@ -1370,33 +1478,39 @@
         <v>50</v>
       </c>
       <c r="I17" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="U17" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="T17" s="6" t="inlineStr">
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>72.67%</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V17" s="9" t="inlineStr">
+      <c r="X17" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1413,52 +1527,62 @@
           <t>Suraj Kumar Singh</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Niraj Singh</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>25-Jun-2017</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" s="10" t="n">
+      <c r="F18" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G18" s="10" t="n">
+      <c r="H18" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I18" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="H18" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I18" s="10" t="n">
+      <c r="J18" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K18" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="10" t="n"/>
       <c r="N18" s="10" t="n"/>
       <c r="O18" s="10" t="n"/>
       <c r="P18" s="10" t="n"/>
       <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="10" t="n">
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="U18" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="T18" s="10" t="inlineStr">
+      <c r="V18" s="10" t="inlineStr">
         <is>
           <t>80.67%</t>
         </is>
       </c>
-      <c r="U18" s="13" t="inlineStr">
+      <c r="W18" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V18" s="12" t="inlineStr">
+      <c r="X18" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1475,20 +1599,24 @@
           <t>Stuti Sikandar</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Sikandar Kumar Das</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>25-Feb-2017</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="6" t="n">
         <v>42</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>35</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>50</v>
@@ -1496,31 +1624,37 @@
       <c r="I19" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>35</v>
+      </c>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="U19" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="T19" s="6" t="inlineStr">
+      <c r="V19" s="6" t="inlineStr">
         <is>
           <t>74.67%</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V19" s="9" t="inlineStr">
+      <c r="X19" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1537,14 +1671,18 @@
           <t>Harsh Kumar</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Chandan Das</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>04-Dec-2017</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>6</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>35</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>50</v>
@@ -1556,33 +1694,39 @@
         <v>50</v>
       </c>
       <c r="I20" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
       <c r="Q20" s="10" t="n"/>
-      <c r="R20" s="10" t="n">
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="S20" s="10" t="n">
+      <c r="U20" s="10" t="n">
         <v>106</v>
       </c>
-      <c r="T20" s="10" t="inlineStr">
+      <c r="V20" s="10" t="inlineStr">
         <is>
           <t>70.67%</t>
         </is>
       </c>
-      <c r="U20" s="13" t="inlineStr">
+      <c r="W20" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V20" s="12" t="inlineStr">
+      <c r="X20" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1611,6 +1755,8 @@
       <c r="T21" s="16" t="n"/>
       <c r="U21" s="16" t="n"/>
       <c r="V21" s="16" t="n"/>
+      <c r="W21" s="16" t="n"/>
+      <c r="X21" s="16" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1630,56 +1776,66 @@
           <t>Prasant Kumar Tiwari</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Rakesh Tiwari</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>14-Oct-2016</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H23" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I23" s="6" t="n">
+      <c r="J23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K23" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="J23" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K23" s="6" t="n">
+      <c r="L23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M23" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
+      <c r="T23" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="U23" s="6" t="n">
         <v>169</v>
       </c>
-      <c r="T23" s="6" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>84.50%</t>
         </is>
       </c>
-      <c r="U23" s="9" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V23" s="9" t="inlineStr">
+      <c r="X23" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1696,20 +1852,24 @@
           <t>Piyush Kumar</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Parmeshwar Kumar</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>10-Jan-2016</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="F24" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" s="10" t="n">
         <v>39</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>45</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>50</v>
@@ -1721,31 +1881,37 @@
         <v>50</v>
       </c>
       <c r="K24" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="L24" s="10" t="n"/>
-      <c r="M24" s="10" t="n"/>
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
       <c r="Q24" s="10" t="n"/>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S24" s="10" t="n">
+      <c r="U24" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="T24" s="10" t="inlineStr">
+      <c r="V24" s="10" t="inlineStr">
         <is>
           <t>87.50%</t>
         </is>
       </c>
-      <c r="U24" s="12" t="inlineStr">
+      <c r="W24" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V24" s="12" t="inlineStr">
+      <c r="X24" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1762,56 +1928,66 @@
           <t>Supriya Bharti</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Krishna Kumar Das</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>02-Feb-2017</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="H25" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I25" s="6" t="n">
+      <c r="J25" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K25" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="J25" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K25" s="6" t="n">
+      <c r="L25" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M25" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
       <c r="N25" s="6" t="n"/>
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n"/>
+      <c r="T25" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="U25" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="T25" s="6" t="inlineStr">
+      <c r="V25" s="6" t="inlineStr">
         <is>
           <t>64.00%</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="W25" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V25" s="9" t="inlineStr">
+      <c r="X25" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1828,56 +2004,66 @@
           <t>Akash Raj</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar Das</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>13-Jun-2017</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E26" s="10" t="n">
+      <c r="F26" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G26" s="10" t="n">
+      <c r="H26" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="H26" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I26" s="10" t="n">
+      <c r="J26" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K26" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="J26" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K26" s="10" t="n">
+      <c r="L26" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M26" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="L26" s="10" t="n"/>
-      <c r="M26" s="10" t="n"/>
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
       <c r="Q26" s="10" t="n"/>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S26" s="10" t="n">
+      <c r="U26" s="10" t="n">
         <v>112</v>
       </c>
-      <c r="T26" s="10" t="inlineStr">
+      <c r="V26" s="10" t="inlineStr">
         <is>
           <t>56.00%</t>
         </is>
       </c>
-      <c r="U26" s="15" t="inlineStr">
+      <c r="W26" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V26" s="12" t="inlineStr">
+      <c r="X26" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1894,56 +2080,66 @@
           <t>Kiran Kumari</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Chandan Das</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>20-Jun-2016</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I27" s="6" t="n">
+      <c r="J27" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K27" s="6" t="n">
+      <c r="L27" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M27" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
       <c r="N27" s="6" t="n"/>
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
+      <c r="T27" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="U27" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="T27" s="6" t="inlineStr">
+      <c r="V27" s="6" t="inlineStr">
         <is>
           <t>59.50%</t>
         </is>
       </c>
-      <c r="U27" s="14" t="inlineStr">
+      <c r="W27" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V27" s="9" t="inlineStr">
+      <c r="X27" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1972,6 +2168,8 @@
       <c r="T28" s="16" t="n"/>
       <c r="U28" s="16" t="n"/>
       <c r="V28" s="16" t="n"/>
+      <c r="W28" s="16" t="n"/>
+      <c r="X28" s="16" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -1991,56 +2189,66 @@
           <t>Shambhavi Kumari</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Arvind Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>22-Jun-2019</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I30" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H30" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I30" s="6" t="n">
+      <c r="J30" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="J30" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K30" s="6" t="n">
+      <c r="L30" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M30" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
       <c r="N30" s="6" t="n"/>
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n">
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="6" t="n"/>
+      <c r="T30" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="U30" s="6" t="n">
         <v>179</v>
       </c>
-      <c r="T30" s="6" t="inlineStr">
+      <c r="V30" s="6" t="inlineStr">
         <is>
           <t>89.50%</t>
         </is>
       </c>
-      <c r="U30" s="9" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V30" s="9" t="inlineStr">
+      <c r="X30" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2057,56 +2265,66 @@
           <t>Riddhi Kumari</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Vikash Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>28-Sep-2016</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E31" s="10" t="n">
+      <c r="F31" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G31" s="10" t="n">
+      <c r="H31" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="H31" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I31" s="10" t="n">
+      <c r="J31" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K31" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="J31" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K31" s="10" t="n">
+      <c r="L31" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M31" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n"/>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
       <c r="Q31" s="10" t="n"/>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S31" s="10" t="n">
+      <c r="U31" s="10" t="n">
         <v>165</v>
       </c>
-      <c r="T31" s="10" t="inlineStr">
+      <c r="V31" s="10" t="inlineStr">
         <is>
           <t>82.50%</t>
         </is>
       </c>
-      <c r="U31" s="12" t="inlineStr">
+      <c r="W31" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V31" s="12" t="inlineStr">
+      <c r="X31" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2123,20 +2341,24 @@
           <t>Siddhi Kumari</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Vikash Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>28-Sep-2016</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="6" t="n">
         <v>45</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>46</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>50</v>
@@ -2148,31 +2370,37 @@
         <v>50</v>
       </c>
       <c r="K32" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M32" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
       <c r="N32" s="6" t="n"/>
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="n">
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="n"/>
+      <c r="T32" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S32" s="6" t="n">
+      <c r="U32" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="T32" s="6" t="inlineStr">
+      <c r="V32" s="6" t="inlineStr">
         <is>
           <t>88.50%</t>
         </is>
       </c>
-      <c r="U32" s="9" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V32" s="9" t="inlineStr">
+      <c r="X32" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2189,56 +2417,66 @@
           <t>Ranvir Kumar</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Chandan Modi</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>02-May-2016</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E33" s="10" t="n">
+      <c r="F33" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G33" s="10" t="n">
+      <c r="H33" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I33" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="H33" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I33" s="10" t="n">
+      <c r="J33" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="J33" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K33" s="10" t="n">
+      <c r="L33" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M33" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
       <c r="Q33" s="10" t="n"/>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S33" s="10" t="n">
+      <c r="U33" s="10" t="n">
         <v>138</v>
       </c>
-      <c r="T33" s="10" t="inlineStr">
+      <c r="V33" s="10" t="inlineStr">
         <is>
           <t>69.00%</t>
         </is>
       </c>
-      <c r="U33" s="13" t="inlineStr">
+      <c r="W33" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V33" s="12" t="inlineStr">
+      <c r="X33" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2255,56 +2493,66 @@
           <t>Priti Kumari</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Kapildev Das</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>13-Jun-2015</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I34" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="H34" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I34" s="6" t="n">
+      <c r="J34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K34" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J34" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K34" s="6" t="n">
+      <c r="L34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="L34" s="6" t="n"/>
-      <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n"/>
       <c r="O34" s="6" t="n"/>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n"/>
-      <c r="R34" s="6" t="n">
+      <c r="R34" s="6" t="n"/>
+      <c r="S34" s="6" t="n"/>
+      <c r="T34" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S34" s="6" t="n">
+      <c r="U34" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="T34" s="6" t="inlineStr">
+      <c r="V34" s="6" t="inlineStr">
         <is>
           <t>63.00%</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V34" s="9" t="inlineStr">
+      <c r="X34" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2321,26 +2569,30 @@
           <t>Priyanshu Kumar</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Amit Tiwari</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>02-Oct-2016</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E35" s="10" t="n">
+      <c r="F35" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G35" s="10" t="n">
+      <c r="H35" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" s="10" t="n">
         <v>22</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>30</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>50</v>
@@ -2348,29 +2600,35 @@
       <c r="K35" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="L35" s="10" t="n"/>
-      <c r="M35" s="10" t="n"/>
+      <c r="L35" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>30</v>
+      </c>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
       <c r="P35" s="10" t="n"/>
       <c r="Q35" s="10" t="n"/>
-      <c r="R35" s="10" t="n">
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S35" s="10" t="n">
+      <c r="U35" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="T35" s="10" t="inlineStr">
+      <c r="V35" s="10" t="inlineStr">
         <is>
           <t>54.50%</t>
         </is>
       </c>
-      <c r="U35" s="15" t="inlineStr">
+      <c r="W35" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V35" s="12" t="inlineStr">
+      <c r="X35" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2387,56 +2645,66 @@
           <t>Sumit Kumar</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Chuhan Tanti</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>15-Oct-2016</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G36" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="F36" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H36" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I36" s="6" t="n">
+      <c r="J36" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K36" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="J36" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K36" s="6" t="n">
+      <c r="L36" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M36" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L36" s="6" t="n"/>
-      <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n"/>
       <c r="O36" s="6" t="n"/>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n"/>
-      <c r="R36" s="6" t="n">
+      <c r="R36" s="6" t="n"/>
+      <c r="S36" s="6" t="n"/>
+      <c r="T36" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S36" s="6" t="n">
+      <c r="U36" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="T36" s="6" t="inlineStr">
+      <c r="V36" s="6" t="inlineStr">
         <is>
           <t>71.00%</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="W36" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V36" s="9" t="inlineStr">
+      <c r="X36" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2453,26 +2721,30 @@
           <t>Ankit Kumar</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Krishna Tanti</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>01-Jan-2016</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E37" s="10" t="n">
+      <c r="F37" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G37" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G37" s="10" t="n">
+      <c r="H37" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" s="10" t="n">
         <v>30</v>
-      </c>
-      <c r="H37" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I37" s="10" t="n">
-        <v>40</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>50</v>
@@ -2480,29 +2752,35 @@
       <c r="K37" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
+      <c r="L37" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>40</v>
+      </c>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
       <c r="P37" s="10" t="n"/>
       <c r="Q37" s="10" t="n"/>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S37" s="10" t="n">
+      <c r="U37" s="10" t="n">
         <v>142</v>
       </c>
-      <c r="T37" s="10" t="inlineStr">
+      <c r="V37" s="10" t="inlineStr">
         <is>
           <t>71.00%</t>
         </is>
       </c>
-      <c r="U37" s="13" t="inlineStr">
+      <c r="W37" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V37" s="12" t="inlineStr">
+      <c r="X37" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2519,56 +2797,66 @@
           <t>Anshika Kumari</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Avadhesh Dubey</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>11-Oct-2015</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E38" s="10" t="n">
+      <c r="F38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G38" s="10" t="n">
+      <c r="H38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="H38" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I38" s="10" t="n">
+      <c r="J38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K38" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="J38" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K38" s="10" t="n">
+      <c r="L38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M38" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="L38" s="10" t="n"/>
-      <c r="M38" s="10" t="n"/>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="n"/>
       <c r="P38" s="10" t="n"/>
       <c r="Q38" s="10" t="n"/>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S38" s="10" t="n">
+      <c r="U38" s="10" t="n">
         <v>166</v>
       </c>
-      <c r="T38" s="10" t="inlineStr">
+      <c r="V38" s="10" t="inlineStr">
         <is>
           <t>83.00%</t>
         </is>
       </c>
-      <c r="U38" s="12" t="inlineStr">
+      <c r="W38" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V38" s="12" t="inlineStr">
+      <c r="X38" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2585,14 +2873,18 @@
           <t>Chintu Kumar</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Babu Lal Ravidas</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>14-Jan-2012</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
         <v>11</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>50</v>
@@ -2610,31 +2902,37 @@
         <v>50</v>
       </c>
       <c r="K39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M39" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="L39" s="6" t="n"/>
-      <c r="M39" s="6" t="n"/>
       <c r="N39" s="6" t="n"/>
       <c r="O39" s="6" t="n"/>
       <c r="P39" s="6" t="n"/>
       <c r="Q39" s="6" t="n"/>
-      <c r="R39" s="6" t="n">
+      <c r="R39" s="6" t="n"/>
+      <c r="S39" s="6" t="n"/>
+      <c r="T39" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S39" s="6" t="n">
+      <c r="U39" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="T39" s="6" t="inlineStr">
+      <c r="V39" s="6" t="inlineStr">
         <is>
           <t>14.00%</t>
         </is>
       </c>
-      <c r="U39" s="17" t="inlineStr">
+      <c r="W39" s="17" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="V39" s="17" t="inlineStr">
+      <c r="X39" s="17" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -2663,6 +2961,8 @@
       <c r="T40" s="16" t="n"/>
       <c r="U40" s="16" t="n"/>
       <c r="V40" s="16" t="n"/>
+      <c r="W40" s="16" t="n"/>
+      <c r="X40" s="16" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -2682,56 +2982,66 @@
           <t>Amardeep Kumar</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Arvind Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>15-Sep-2015</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I42" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H42" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I42" s="6" t="n">
+      <c r="J42" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K42" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J42" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K42" s="6" t="n">
+      <c r="L42" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M42" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="L42" s="6" t="n"/>
-      <c r="M42" s="6" t="n"/>
       <c r="N42" s="6" t="n"/>
       <c r="O42" s="6" t="n"/>
       <c r="P42" s="6" t="n"/>
       <c r="Q42" s="6" t="n"/>
-      <c r="R42" s="6" t="n">
+      <c r="R42" s="6" t="n"/>
+      <c r="S42" s="6" t="n"/>
+      <c r="T42" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S42" s="6" t="n">
+      <c r="U42" s="6" t="n">
         <v>175</v>
       </c>
-      <c r="T42" s="6" t="inlineStr">
+      <c r="V42" s="6" t="inlineStr">
         <is>
           <t>87.50%</t>
         </is>
       </c>
-      <c r="U42" s="9" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V42" s="9" t="inlineStr">
+      <c r="X42" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2748,56 +3058,66 @@
           <t>Devraj Kumar Tiwari</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Tiwari</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>10-Jul-2015</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E43" s="10" t="n">
+      <c r="F43" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G43" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G43" s="10" t="n">
+      <c r="H43" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I43" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="H43" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I43" s="10" t="n">
+      <c r="J43" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K43" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="J43" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K43" s="10" t="n">
+      <c r="L43" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M43" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
       <c r="P43" s="10" t="n"/>
       <c r="Q43" s="10" t="n"/>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="U43" s="10" t="n">
         <v>171</v>
       </c>
-      <c r="T43" s="10" t="inlineStr">
+      <c r="V43" s="10" t="inlineStr">
         <is>
           <t>85.50%</t>
         </is>
       </c>
-      <c r="U43" s="12" t="inlineStr">
+      <c r="W43" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V43" s="12" t="inlineStr">
+      <c r="X43" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2814,56 +3134,66 @@
           <t>Anshu Kumar</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Manoj Ravidas</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>27-Jun-2014</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D44" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G44" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="H44" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I44" s="6" t="n">
+      <c r="J44" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K44" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="J44" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K44" s="6" t="n">
+      <c r="L44" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M44" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="L44" s="6" t="n"/>
-      <c r="M44" s="6" t="n"/>
       <c r="N44" s="6" t="n"/>
       <c r="O44" s="6" t="n"/>
       <c r="P44" s="6" t="n"/>
       <c r="Q44" s="6" t="n"/>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="6" t="n"/>
+      <c r="S44" s="6" t="n"/>
+      <c r="T44" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S44" s="6" t="n">
+      <c r="U44" s="6" t="n">
         <v>143</v>
       </c>
-      <c r="T44" s="6" t="inlineStr">
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>71.50%</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="W44" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V44" s="9" t="inlineStr">
+      <c r="X44" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2880,56 +3210,66 @@
           <t>Sabita Kumari</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Manohar Tanti</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>28-Mar-2015</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E45" s="10" t="n">
+      <c r="F45" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G45" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G45" s="10" t="n">
+      <c r="H45" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I45" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H45" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I45" s="10" t="n">
+      <c r="J45" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K45" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="J45" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K45" s="10" t="n">
+      <c r="L45" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M45" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
       <c r="P45" s="10" t="n"/>
       <c r="Q45" s="10" t="n"/>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S45" s="10" t="n">
+      <c r="U45" s="10" t="n">
         <v>167</v>
       </c>
-      <c r="T45" s="10" t="inlineStr">
+      <c r="V45" s="10" t="inlineStr">
         <is>
           <t>83.50%</t>
         </is>
       </c>
-      <c r="U45" s="12" t="inlineStr">
+      <c r="W45" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V45" s="12" t="inlineStr">
+      <c r="X45" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2946,56 +3286,66 @@
           <t>Sonu Kumar Tiwari</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Anjani Tiwari</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>20-Jun-2015</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E46" s="6" t="n">
+      <c r="F46" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G46" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="F46" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G46" s="6" t="n">
+      <c r="H46" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="H46" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I46" s="6" t="n">
+      <c r="J46" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K46" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K46" s="6" t="n">
+      <c r="L46" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M46" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="L46" s="6" t="n"/>
-      <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n"/>
       <c r="O46" s="6" t="n"/>
       <c r="P46" s="6" t="n"/>
       <c r="Q46" s="6" t="n"/>
-      <c r="R46" s="6" t="n">
+      <c r="R46" s="6" t="n"/>
+      <c r="S46" s="6" t="n"/>
+      <c r="T46" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S46" s="6" t="n">
+      <c r="U46" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="T46" s="6" t="inlineStr">
+      <c r="V46" s="6" t="inlineStr">
         <is>
           <t>75.00%</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="W46" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V46" s="9" t="inlineStr">
+      <c r="X46" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3012,56 +3362,66 @@
           <t>Anushka Kumari</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Onkar Kumar Das</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>12-Apr-2015</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D47" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E47" s="10" t="n">
+      <c r="F47" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G47" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G47" s="10" t="n">
+      <c r="H47" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I47" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H47" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I47" s="10" t="n">
+      <c r="J47" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K47" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="J47" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K47" s="10" t="n">
+      <c r="L47" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M47" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="n"/>
       <c r="N47" s="10" t="n"/>
       <c r="O47" s="10" t="n"/>
       <c r="P47" s="10" t="n"/>
       <c r="Q47" s="10" t="n"/>
-      <c r="R47" s="10" t="n">
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S47" s="10" t="n">
+      <c r="U47" s="10" t="n">
         <v>149</v>
       </c>
-      <c r="T47" s="10" t="inlineStr">
+      <c r="V47" s="10" t="inlineStr">
         <is>
           <t>74.50%</t>
         </is>
       </c>
-      <c r="U47" s="13" t="inlineStr">
+      <c r="W47" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V47" s="12" t="inlineStr">
+      <c r="X47" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3078,20 +3438,24 @@
           <t>Amit Kumar</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Chuhan Tanti</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>10-Aug-2015</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D48" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E48" s="6" t="n">
+      <c r="F48" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G48" s="6" t="n">
         <v>31</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>25</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>50</v>
@@ -3103,31 +3467,37 @@
         <v>50</v>
       </c>
       <c r="K48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M48" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n"/>
       <c r="O48" s="6" t="n"/>
       <c r="P48" s="6" t="n"/>
       <c r="Q48" s="6" t="n"/>
-      <c r="R48" s="6" t="n">
+      <c r="R48" s="6" t="n"/>
+      <c r="S48" s="6" t="n"/>
+      <c r="T48" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="S48" s="6" t="n">
+      <c r="U48" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="T48" s="6" t="inlineStr">
+      <c r="V48" s="6" t="inlineStr">
         <is>
           <t>59.00%</t>
         </is>
       </c>
-      <c r="U48" s="14" t="inlineStr">
+      <c r="W48" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V48" s="9" t="inlineStr">
+      <c r="X48" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3144,20 +3514,24 @@
           <t>Sapna Kumari</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Shambhu Tanti</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>12-Sep-2015</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D49" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E49" s="10" t="n">
+      <c r="F49" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G49" s="10" t="n">
         <v>25</v>
-      </c>
-      <c r="F49" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G49" s="10" t="n">
-        <v>22</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>50</v>
@@ -3169,31 +3543,37 @@
         <v>50</v>
       </c>
       <c r="K49" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L49" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M49" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
       <c r="P49" s="10" t="n"/>
       <c r="Q49" s="10" t="n"/>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="U49" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="T49" s="10" t="inlineStr">
+      <c r="V49" s="10" t="inlineStr">
         <is>
           <t>46.00%</t>
         </is>
       </c>
-      <c r="U49" s="15" t="inlineStr">
+      <c r="W49" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V49" s="12" t="inlineStr">
+      <c r="X49" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3222,6 +3602,8 @@
       <c r="T50" s="16" t="n"/>
       <c r="U50" s="16" t="n"/>
       <c r="V50" s="16" t="n"/>
+      <c r="W50" s="16" t="n"/>
+      <c r="X50" s="16" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -3241,64 +3623,74 @@
           <t>Ayushi Kumari</t>
         </is>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Prakash Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>26-Apr-2014</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E52" s="6" t="n">
+      <c r="F52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F52" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" s="6" t="n">
+      <c r="H52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="H52" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I52" s="6" t="n">
+      <c r="J52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K52" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M52" s="6" t="n">
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O52" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O52" s="6" t="n">
+      <c r="P52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q52" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="P52" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q52" s="6" t="n">
+      <c r="R52" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S52" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R52" s="6" t="n">
+      <c r="T52" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S52" s="6" t="n">
+      <c r="U52" s="6" t="n">
         <v>267</v>
       </c>
-      <c r="T52" s="6" t="inlineStr">
+      <c r="V52" s="6" t="inlineStr">
         <is>
           <t>89.00%</t>
         </is>
       </c>
-      <c r="U52" s="9" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V52" s="9" t="inlineStr">
+      <c r="X52" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3315,64 +3707,74 @@
           <t>Santanu Kumar Tiwari</t>
         </is>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Anjani Tiwari</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>20-Jun-2013</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D53" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E53" s="10" t="n">
+      <c r="F53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G53" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G53" s="10" t="n">
+      <c r="H53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="H53" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" s="10" t="n">
+      <c r="J53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K53" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M53" s="10" t="n">
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O53" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="N53" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O53" s="10" t="n">
+      <c r="P53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q53" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="P53" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q53" s="10" t="n">
+      <c r="R53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S53" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="R53" s="10" t="n">
+      <c r="T53" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S53" s="10" t="n">
+      <c r="U53" s="10" t="n">
         <v>279</v>
       </c>
-      <c r="T53" s="10" t="inlineStr">
+      <c r="V53" s="10" t="inlineStr">
         <is>
           <t>93.00%</t>
         </is>
       </c>
-      <c r="U53" s="12" t="inlineStr">
+      <c r="W53" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V53" s="12" t="inlineStr">
+      <c r="X53" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3389,64 +3791,74 @@
           <t>Balram Kumar Tiwari</t>
         </is>
       </c>
-      <c r="C54" s="6" t="n">
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Tiwari</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>21-Jun-2013</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E54" s="6" t="n">
+      <c r="F54" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G54" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F54" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G54" s="6" t="n">
+      <c r="H54" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H54" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I54" s="6" t="n">
+      <c r="J54" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K54" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M54" s="6" t="n">
+      <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
+      <c r="N54" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O54" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O54" s="6" t="n">
+      <c r="P54" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q54" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="P54" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q54" s="6" t="n">
+      <c r="R54" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S54" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R54" s="6" t="n">
+      <c r="T54" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S54" s="6" t="n">
+      <c r="U54" s="6" t="n">
         <v>252</v>
       </c>
-      <c r="T54" s="6" t="inlineStr">
+      <c r="V54" s="6" t="inlineStr">
         <is>
           <t>84.00%</t>
         </is>
       </c>
-      <c r="U54" s="9" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V54" s="9" t="inlineStr">
+      <c r="X54" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3463,64 +3875,74 @@
           <t>Jyoti Kumari</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar Das</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>28-Aug-2013</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E55" s="10" t="n">
+      <c r="F55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G55" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G55" s="10" t="n">
+      <c r="H55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="H55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I55" s="10" t="n">
+      <c r="J55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K55" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M55" s="10" t="n">
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O55" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="N55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O55" s="10" t="n">
+      <c r="P55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q55" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="P55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q55" s="10" t="n">
+      <c r="R55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S55" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="R55" s="10" t="n">
+      <c r="T55" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S55" s="10" t="n">
+      <c r="U55" s="10" t="n">
         <v>246</v>
       </c>
-      <c r="T55" s="10" t="inlineStr">
+      <c r="V55" s="10" t="inlineStr">
         <is>
           <t>82.00%</t>
         </is>
       </c>
-      <c r="U55" s="12" t="inlineStr">
+      <c r="W55" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V55" s="12" t="inlineStr">
+      <c r="X55" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3537,64 +3959,74 @@
           <t>Ankit Kumar</t>
         </is>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Parmeshwar Das</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>13-Oct-2013</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E56" s="6" t="n">
+      <c r="F56" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G56" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F56" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G56" s="6" t="n">
+      <c r="H56" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="H56" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I56" s="6" t="n">
+      <c r="J56" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K56" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="J56" s="6" t="n"/>
-      <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M56" s="6" t="n">
+      <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
+      <c r="N56" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O56" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O56" s="6" t="n">
+      <c r="P56" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q56" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="P56" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q56" s="6" t="n">
+      <c r="R56" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S56" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R56" s="6" t="n">
+      <c r="T56" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S56" s="6" t="n">
+      <c r="U56" s="6" t="n">
         <v>221</v>
       </c>
-      <c r="T56" s="6" t="inlineStr">
+      <c r="V56" s="6" t="inlineStr">
         <is>
           <t>73.67%</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="W56" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V56" s="9" t="inlineStr">
+      <c r="X56" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3611,64 +4043,74 @@
           <t>Gopi Kumar</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Bacchu Tanti</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>20-Aug-2013</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E57" s="10" t="n">
+      <c r="F57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G57" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="F57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G57" s="10" t="n">
+      <c r="H57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I57" s="10" t="n">
+      <c r="J57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K57" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M57" s="10" t="n">
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O57" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="N57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O57" s="10" t="n">
+      <c r="P57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q57" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="P57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q57" s="10" t="n">
+      <c r="R57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S57" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="R57" s="10" t="n">
+      <c r="T57" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S57" s="10" t="n">
+      <c r="U57" s="10" t="n">
         <v>231</v>
       </c>
-      <c r="T57" s="10" t="inlineStr">
+      <c r="V57" s="10" t="inlineStr">
         <is>
           <t>77.00%</t>
         </is>
       </c>
-      <c r="U57" s="13" t="inlineStr">
+      <c r="W57" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V57" s="12" t="inlineStr">
+      <c r="X57" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3685,64 +4127,74 @@
           <t>Savitri Kumari</t>
         </is>
       </c>
-      <c r="C58" s="6" t="n">
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Sambhu Tanti</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>25-Aug-2013</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D58" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E58" s="6" t="n">
+      <c r="F58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="F58" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G58" s="6" t="n">
+      <c r="H58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="H58" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I58" s="6" t="n">
+      <c r="J58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K58" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J58" s="6" t="n"/>
-      <c r="K58" s="6" t="n"/>
-      <c r="L58" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M58" s="6" t="n">
+      <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
+      <c r="N58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O58" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O58" s="6" t="n">
+      <c r="P58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q58" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q58" s="6" t="n">
+      <c r="R58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S58" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="R58" s="6" t="n">
+      <c r="T58" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S58" s="6" t="n">
+      <c r="U58" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="T58" s="6" t="inlineStr">
+      <c r="V58" s="6" t="inlineStr">
         <is>
           <t>80.00%</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="W58" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V58" s="9" t="inlineStr">
+      <c r="X58" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3759,64 +4211,74 @@
           <t>Dharamraj Kumar</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Banavari Manjhi</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>09-Feb-2013</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E59" s="10" t="n">
+      <c r="F59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G59" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G59" s="10" t="n">
+      <c r="H59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I59" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="H59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I59" s="10" t="n">
+      <c r="J59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K59" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M59" s="10" t="n">
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O59" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="N59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O59" s="10" t="n">
+      <c r="P59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q59" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="P59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q59" s="10" t="n">
+      <c r="R59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S59" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R59" s="10" t="n">
+      <c r="T59" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S59" s="10" t="n">
+      <c r="U59" s="10" t="n">
         <v>215</v>
       </c>
-      <c r="T59" s="10" t="inlineStr">
+      <c r="V59" s="10" t="inlineStr">
         <is>
           <t>71.67%</t>
         </is>
       </c>
-      <c r="U59" s="13" t="inlineStr">
+      <c r="W59" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V59" s="12" t="inlineStr">
+      <c r="X59" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3833,64 +4295,74 @@
           <t>Rishi Raj</t>
         </is>
       </c>
-      <c r="C60" s="6" t="n">
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Priy Ranjan Singh</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>27-Jul-2014</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E60" s="6" t="n">
+      <c r="F60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G60" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G60" s="6" t="n">
+      <c r="H60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="H60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I60" s="6" t="n">
+      <c r="J60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K60" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M60" s="6" t="n">
+      <c r="L60" s="6" t="n"/>
+      <c r="M60" s="6" t="n"/>
+      <c r="N60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O60" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="N60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O60" s="6" t="n">
+      <c r="P60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q60" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="P60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q60" s="6" t="n">
+      <c r="R60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S60" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="R60" s="6" t="n">
+      <c r="T60" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S60" s="6" t="n">
+      <c r="U60" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="T60" s="6" t="inlineStr">
+      <c r="V60" s="6" t="inlineStr">
         <is>
           <t>84.33%</t>
         </is>
       </c>
-      <c r="U60" s="9" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V60" s="9" t="inlineStr">
+      <c r="X60" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3907,35 +4379,39 @@
           <t>Abhinash Kumar</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Ajit Rawat</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>02-Aug-2014</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D61" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E61" s="10" t="n">
+      <c r="F61" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G61" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="F61" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G61" s="10" t="n">
+      <c r="H61" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="H61" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I61" s="10" t="n">
+      <c r="J61" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K61" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M61" s="10" t="n">
-        <v>42</v>
-      </c>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
       <c r="N61" s="10" t="n">
         <v>50</v>
       </c>
@@ -3946,25 +4422,31 @@
         <v>50</v>
       </c>
       <c r="Q61" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="R61" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S61" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="R61" s="10" t="n">
+      <c r="T61" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S61" s="10" t="n">
+      <c r="U61" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="T61" s="10" t="inlineStr">
+      <c r="V61" s="10" t="inlineStr">
         <is>
           <t>83.33%</t>
         </is>
       </c>
-      <c r="U61" s="12" t="inlineStr">
+      <c r="W61" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V61" s="12" t="inlineStr">
+      <c r="X61" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3981,20 +4463,24 @@
           <t>Raj Kumar</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Jitendra Rawat</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>05-Jun-2013</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D62" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E62" s="6" t="n">
+      <c r="F62" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G62" s="6" t="n">
         <v>37</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>41</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>50</v>
@@ -4002,43 +4488,49 @@
       <c r="I62" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M62" s="6" t="n">
+      <c r="J62" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K62" s="6" t="n">
         <v>41</v>
       </c>
+      <c r="L62" s="6" t="n"/>
+      <c r="M62" s="6" t="n"/>
       <c r="N62" s="6" t="n">
         <v>50</v>
       </c>
       <c r="O62" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q62" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="P62" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q62" s="6" t="n">
+      <c r="R62" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S62" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="R62" s="6" t="n">
+      <c r="T62" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S62" s="6" t="n">
+      <c r="U62" s="6" t="n">
         <v>241</v>
       </c>
-      <c r="T62" s="6" t="inlineStr">
+      <c r="V62" s="6" t="inlineStr">
         <is>
           <t>80.33%</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
+      <c r="W62" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V62" s="9" t="inlineStr">
+      <c r="X62" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4055,64 +4547,74 @@
           <t>Kanhaiya Kumar</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Ramkhailawan Tanti</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>18-Aug-2014</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D63" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E63" s="10" t="n">
+      <c r="F63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G63" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="F63" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G63" s="10" t="n">
+      <c r="H63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I63" s="10" t="n">
+      <c r="J63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K63" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
-      <c r="L63" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M63" s="10" t="n">
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O63" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="N63" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O63" s="10" t="n">
+      <c r="P63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q63" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="P63" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q63" s="10" t="n">
+      <c r="R63" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S63" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R63" s="10" t="n">
+      <c r="T63" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S63" s="10" t="n">
+      <c r="U63" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="T63" s="10" t="inlineStr">
+      <c r="V63" s="10" t="inlineStr">
         <is>
           <t>66.67%</t>
         </is>
       </c>
-      <c r="U63" s="13" t="inlineStr">
+      <c r="W63" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V63" s="18" t="inlineStr">
+      <c r="X63" s="18" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4129,64 +4631,74 @@
           <t>Rani Kumari</t>
         </is>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Ramchandra Rawat</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>20-Jun-2014</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D64" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E64" s="6" t="n">
+      <c r="F64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G64" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F64" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G64" s="6" t="n">
+      <c r="H64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="H64" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I64" s="6" t="n">
+      <c r="J64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K64" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M64" s="6" t="n">
+      <c r="L64" s="6" t="n"/>
+      <c r="M64" s="6" t="n"/>
+      <c r="N64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O64" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="N64" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O64" s="6" t="n">
+      <c r="P64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q64" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q64" s="6" t="n">
+      <c r="R64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S64" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="R64" s="6" t="n">
+      <c r="T64" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S64" s="6" t="n">
+      <c r="U64" s="6" t="n">
         <v>196</v>
       </c>
-      <c r="T64" s="6" t="inlineStr">
+      <c r="V64" s="6" t="inlineStr">
         <is>
           <t>65.33%</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
+      <c r="W64" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V64" s="9" t="inlineStr">
+      <c r="X64" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4203,64 +4715,74 @@
           <t>Krishama Kumari</t>
         </is>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Mannu Rawat</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>01-Sep-2013</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E65" s="10" t="n">
+      <c r="F65" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G65" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="F65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G65" s="10" t="n">
+      <c r="H65" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I65" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="H65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I65" s="10" t="n">
+      <c r="J65" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K65" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M65" s="10" t="n">
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O65" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="N65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O65" s="10" t="n">
+      <c r="P65" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q65" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="P65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q65" s="10" t="n">
+      <c r="R65" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S65" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R65" s="10" t="n">
+      <c r="T65" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S65" s="10" t="n">
+      <c r="U65" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="T65" s="10" t="inlineStr">
+      <c r="V65" s="10" t="inlineStr">
         <is>
           <t>70.67%</t>
         </is>
       </c>
-      <c r="U65" s="13" t="inlineStr">
+      <c r="W65" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V65" s="12" t="inlineStr">
+      <c r="X65" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4277,64 +4799,74 @@
           <t>Shilpa Kumari</t>
         </is>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Papapu Tanti</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>28-Nov-2013</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="D66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E66" s="6" t="n">
+      <c r="F66" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G66" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="F66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G66" s="6" t="n">
+      <c r="H66" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I66" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="H66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I66" s="6" t="n">
+      <c r="J66" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K66" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M66" s="6" t="n">
+      <c r="L66" s="6" t="n"/>
+      <c r="M66" s="6" t="n"/>
+      <c r="N66" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O66" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O66" s="6" t="n">
+      <c r="P66" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q66" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="P66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q66" s="6" t="n">
+      <c r="R66" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S66" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R66" s="6" t="n">
+      <c r="T66" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S66" s="6" t="n">
+      <c r="U66" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="T66" s="6" t="inlineStr">
+      <c r="V66" s="6" t="inlineStr">
         <is>
           <t>83.33%</t>
         </is>
       </c>
-      <c r="U66" s="9" t="inlineStr">
+      <c r="W66" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V66" s="9" t="inlineStr">
+      <c r="X66" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4351,64 +4883,74 @@
           <t>Rubal Raj Singh</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Ranjay Kumar</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>14-Sep-2013</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="D67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E67" s="10" t="n">
+      <c r="F67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G67" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G67" s="10" t="n">
+      <c r="H67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="H67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I67" s="10" t="n">
+      <c r="J67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K67" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M67" s="10" t="n">
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O67" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="N67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O67" s="10" t="n">
+      <c r="P67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q67" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="P67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q67" s="10" t="n">
+      <c r="R67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S67" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R67" s="10" t="n">
+      <c r="T67" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S67" s="10" t="n">
+      <c r="U67" s="10" t="n">
         <v>248</v>
       </c>
-      <c r="T67" s="10" t="inlineStr">
+      <c r="V67" s="10" t="inlineStr">
         <is>
           <t>82.67%</t>
         </is>
       </c>
-      <c r="U67" s="12" t="inlineStr">
+      <c r="W67" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V67" s="12" t="inlineStr">
+      <c r="X67" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4425,64 +4967,74 @@
           <t>Saniya Mirja</t>
         </is>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Surendra Tanti</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>05-Dec-2014</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="D68" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E68" s="6" t="n">
+      <c r="F68" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G68" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="F68" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G68" s="6" t="n">
+      <c r="H68" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H68" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I68" s="6" t="n">
+      <c r="J68" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K68" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M68" s="6" t="n">
+      <c r="L68" s="6" t="n"/>
+      <c r="M68" s="6" t="n"/>
+      <c r="N68" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O68" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="N68" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O68" s="6" t="n">
+      <c r="P68" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q68" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="P68" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q68" s="6" t="n">
+      <c r="R68" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S68" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="R68" s="6" t="n">
+      <c r="T68" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S68" s="6" t="n">
+      <c r="U68" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="T68" s="6" t="inlineStr">
+      <c r="V68" s="6" t="inlineStr">
         <is>
           <t>84.33%</t>
         </is>
       </c>
-      <c r="U68" s="9" t="inlineStr">
+      <c r="W68" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V68" s="9" t="inlineStr">
+      <c r="X68" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4511,6 +5063,8 @@
       <c r="T69" s="16" t="n"/>
       <c r="U69" s="16" t="n"/>
       <c r="V69" s="16" t="n"/>
+      <c r="W69" s="16" t="n"/>
+      <c r="X69" s="16" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -4530,64 +5084,74 @@
           <t>Mosam Kumari</t>
         </is>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Mukesh Das</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>30-Oct-2010</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E71" s="6" t="n">
+      <c r="F71" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G71" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F71" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G71" s="6" t="n">
+      <c r="H71" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I71" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="H71" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I71" s="6" t="n">
+      <c r="J71" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K71" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M71" s="6" t="n">
+      <c r="L71" s="6" t="n"/>
+      <c r="M71" s="6" t="n"/>
+      <c r="N71" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O71" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="N71" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O71" s="6" t="n">
+      <c r="P71" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q71" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="P71" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q71" s="6" t="n">
+      <c r="R71" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S71" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="R71" s="6" t="n">
+      <c r="T71" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S71" s="6" t="n">
+      <c r="U71" s="6" t="n">
         <v>254</v>
       </c>
-      <c r="T71" s="6" t="inlineStr">
+      <c r="V71" s="6" t="inlineStr">
         <is>
           <t>84.67%</t>
         </is>
       </c>
-      <c r="U71" s="9" t="inlineStr">
+      <c r="W71" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V71" s="9" t="inlineStr">
+      <c r="X71" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4604,64 +5168,74 @@
           <t>Anushka Kumari</t>
         </is>
       </c>
-      <c r="C72" s="10" t="n">
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>Gautam Rawat</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>20-Apr-2013</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D72" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E72" s="10" t="n">
+      <c r="F72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G72" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="F72" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G72" s="10" t="n">
+      <c r="H72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I72" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H72" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I72" s="10" t="n">
+      <c r="J72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K72" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="J72" s="10" t="n"/>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M72" s="10" t="n">
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O72" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="N72" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O72" s="10" t="n">
+      <c r="P72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q72" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="P72" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q72" s="10" t="n">
+      <c r="R72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S72" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R72" s="10" t="n">
+      <c r="T72" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S72" s="10" t="n">
+      <c r="U72" s="10" t="n">
         <v>243</v>
       </c>
-      <c r="T72" s="10" t="inlineStr">
+      <c r="V72" s="10" t="inlineStr">
         <is>
           <t>81.00%</t>
         </is>
       </c>
-      <c r="U72" s="12" t="inlineStr">
+      <c r="W72" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V72" s="12" t="inlineStr">
+      <c r="X72" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4678,64 +5252,74 @@
           <t>Chandani Kumari</t>
         </is>
       </c>
-      <c r="C73" s="6" t="n">
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Naresh Dubey</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>15-Jun-2013</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D73" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E73" s="6" t="n">
+      <c r="F73" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G73" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F73" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G73" s="6" t="n">
+      <c r="H73" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H73" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I73" s="6" t="n">
+      <c r="J73" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K73" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M73" s="6" t="n">
+      <c r="L73" s="6" t="n"/>
+      <c r="M73" s="6" t="n"/>
+      <c r="N73" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O73" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="N73" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O73" s="6" t="n">
+      <c r="P73" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q73" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="P73" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q73" s="6" t="n">
+      <c r="R73" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S73" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="R73" s="6" t="n">
+      <c r="T73" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S73" s="6" t="n">
+      <c r="U73" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="T73" s="6" t="inlineStr">
+      <c r="V73" s="6" t="inlineStr">
         <is>
           <t>88.67%</t>
         </is>
       </c>
-      <c r="U73" s="9" t="inlineStr">
+      <c r="W73" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V73" s="9" t="inlineStr">
+      <c r="X73" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4752,35 +5336,39 @@
           <t>Aakarshak Kumar</t>
         </is>
       </c>
-      <c r="C74" s="10" t="n">
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>01-Jan-2012</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D74" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E74" s="10" t="n">
+      <c r="F74" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G74" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F74" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G74" s="10" t="n">
+      <c r="H74" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I74" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="H74" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I74" s="10" t="n">
+      <c r="J74" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K74" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M74" s="10" t="n">
-        <v>44</v>
-      </c>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
       <c r="N74" s="10" t="n">
         <v>50</v>
       </c>
@@ -4791,25 +5379,31 @@
         <v>50</v>
       </c>
       <c r="Q74" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="R74" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S74" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="R74" s="10" t="n">
+      <c r="T74" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S74" s="10" t="n">
+      <c r="U74" s="10" t="n">
         <v>261</v>
       </c>
-      <c r="T74" s="10" t="inlineStr">
+      <c r="V74" s="10" t="inlineStr">
         <is>
           <t>87.00%</t>
         </is>
       </c>
-      <c r="U74" s="12" t="inlineStr">
+      <c r="W74" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V74" s="12" t="inlineStr">
+      <c r="X74" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4826,64 +5420,74 @@
           <t>Sonam Kumari</t>
         </is>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Sunil Rawat</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>02-Feb-2013</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D75" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E75" s="6" t="n">
+      <c r="F75" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G75" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F75" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G75" s="6" t="n">
+      <c r="H75" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I75" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H75" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I75" s="6" t="n">
+      <c r="J75" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K75" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="n"/>
-      <c r="L75" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M75" s="6" t="n">
+      <c r="L75" s="6" t="n"/>
+      <c r="M75" s="6" t="n"/>
+      <c r="N75" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O75" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="N75" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O75" s="6" t="n">
+      <c r="P75" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q75" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="P75" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q75" s="6" t="n">
+      <c r="R75" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S75" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="R75" s="6" t="n">
+      <c r="T75" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S75" s="6" t="n">
+      <c r="U75" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="T75" s="6" t="inlineStr">
+      <c r="V75" s="6" t="inlineStr">
         <is>
           <t>83.33%</t>
         </is>
       </c>
-      <c r="U75" s="9" t="inlineStr">
+      <c r="W75" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V75" s="9" t="inlineStr">
+      <c r="X75" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4900,64 +5504,74 @@
           <t>Karan Kumar</t>
         </is>
       </c>
-      <c r="C76" s="10" t="n">
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>Krishna Kumar Ravidas</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>06-Sep-2013</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D76" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E76" s="10" t="n">
+      <c r="F76" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F76" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G76" s="10" t="n">
+      <c r="H76" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H76" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I76" s="10" t="n">
+      <c r="J76" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K76" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="J76" s="10" t="n"/>
-      <c r="K76" s="10" t="n"/>
-      <c r="L76" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M76" s="10" t="n">
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O76" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="N76" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O76" s="10" t="n">
+      <c r="P76" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q76" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="P76" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q76" s="10" t="n">
+      <c r="R76" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S76" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="R76" s="10" t="n">
+      <c r="T76" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S76" s="10" t="n">
+      <c r="U76" s="10" t="n">
         <v>243</v>
       </c>
-      <c r="T76" s="10" t="inlineStr">
+      <c r="V76" s="10" t="inlineStr">
         <is>
           <t>81.00%</t>
         </is>
       </c>
-      <c r="U76" s="12" t="inlineStr">
+      <c r="W76" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V76" s="12" t="inlineStr">
+      <c r="X76" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4974,64 +5588,74 @@
           <t>Rohit Kumar</t>
         </is>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Amit Tiwari</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>23-Nov-2013</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D77" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E77" s="6" t="n">
+      <c r="F77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G77" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="F77" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G77" s="6" t="n">
+      <c r="H77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="H77" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I77" s="6" t="n">
+      <c r="J77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K77" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="6" t="n"/>
-      <c r="L77" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M77" s="6" t="n">
+      <c r="L77" s="6" t="n"/>
+      <c r="M77" s="6" t="n"/>
+      <c r="N77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O77" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="N77" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O77" s="6" t="n">
+      <c r="P77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q77" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="P77" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q77" s="6" t="n">
+      <c r="R77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S77" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="R77" s="6" t="n">
+      <c r="T77" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S77" s="6" t="n">
+      <c r="U77" s="6" t="n">
         <v>236</v>
       </c>
-      <c r="T77" s="6" t="inlineStr">
+      <c r="V77" s="6" t="inlineStr">
         <is>
           <t>78.67%</t>
         </is>
       </c>
-      <c r="U77" s="8" t="inlineStr">
+      <c r="W77" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V77" s="9" t="inlineStr">
+      <c r="X77" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5048,64 +5672,74 @@
           <t>Ritika Kumari</t>
         </is>
       </c>
-      <c r="C78" s="10" t="n">
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>Bajrangi Rawat</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>31-Dec-2012</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D78" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E78" s="10" t="n">
+      <c r="F78" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G78" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="F78" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G78" s="10" t="n">
+      <c r="H78" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I78" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="H78" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I78" s="10" t="n">
+      <c r="J78" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K78" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M78" s="10" t="n">
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O78" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="N78" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O78" s="10" t="n">
+      <c r="P78" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q78" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="P78" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q78" s="10" t="n">
+      <c r="R78" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S78" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="R78" s="10" t="n">
+      <c r="T78" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S78" s="10" t="n">
+      <c r="U78" s="10" t="n">
         <v>256</v>
       </c>
-      <c r="T78" s="10" t="inlineStr">
+      <c r="V78" s="10" t="inlineStr">
         <is>
           <t>85.33%</t>
         </is>
       </c>
-      <c r="U78" s="12" t="inlineStr">
+      <c r="W78" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V78" s="12" t="inlineStr">
+      <c r="X78" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5122,64 +5756,74 @@
           <t>Pari Kumari</t>
         </is>
       </c>
-      <c r="C79" s="6" t="n">
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Rakesh Tiwari</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>15-Nov-2013</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D79" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E79" s="6" t="n">
+      <c r="F79" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G79" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F79" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G79" s="6" t="n">
+      <c r="H79" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I79" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H79" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I79" s="6" t="n">
+      <c r="J79" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K79" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="6" t="n"/>
-      <c r="L79" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M79" s="6" t="n">
+      <c r="L79" s="6" t="n"/>
+      <c r="M79" s="6" t="n"/>
+      <c r="N79" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O79" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="N79" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O79" s="6" t="n">
+      <c r="P79" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q79" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="P79" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q79" s="6" t="n">
+      <c r="R79" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S79" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="R79" s="6" t="n">
+      <c r="T79" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S79" s="6" t="n">
+      <c r="U79" s="6" t="n">
         <v>209</v>
       </c>
-      <c r="T79" s="6" t="inlineStr">
+      <c r="V79" s="6" t="inlineStr">
         <is>
           <t>69.67%</t>
         </is>
       </c>
-      <c r="U79" s="8" t="inlineStr">
+      <c r="W79" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V79" s="9" t="inlineStr">
+      <c r="X79" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5196,14 +5840,18 @@
           <t>Chunnu Kumar</t>
         </is>
       </c>
-      <c r="C80" s="10" t="n">
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Naresh Dubey</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>15-Jun-2013</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="n">
         <v>10</v>
-      </c>
-      <c r="D80" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>39</v>
       </c>
       <c r="F80" s="10" t="n">
         <v>50</v>
@@ -5215,45 +5863,51 @@
         <v>50</v>
       </c>
       <c r="I80" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K80" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M80" s="10" t="n">
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O80" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="N80" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O80" s="10" t="n">
+      <c r="P80" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q80" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="P80" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q80" s="10" t="n">
+      <c r="R80" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S80" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="R80" s="10" t="n">
+      <c r="T80" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S80" s="10" t="n">
+      <c r="U80" s="10" t="n">
         <v>223</v>
       </c>
-      <c r="T80" s="10" t="inlineStr">
+      <c r="V80" s="10" t="inlineStr">
         <is>
           <t>74.33%</t>
         </is>
       </c>
-      <c r="U80" s="13" t="inlineStr">
+      <c r="W80" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V80" s="12" t="inlineStr">
+      <c r="X80" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5270,35 +5924,39 @@
           <t>Prince Kumar Tiwari</t>
         </is>
       </c>
-      <c r="C81" s="6" t="n">
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Tinku Tiwari</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>10-Aug-2013</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D81" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E81" s="6" t="n">
+      <c r="F81" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G81" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F81" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G81" s="6" t="n">
+      <c r="H81" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I81" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="H81" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I81" s="6" t="n">
+      <c r="J81" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K81" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="6" t="n"/>
-      <c r="L81" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M81" s="6" t="n">
-        <v>42</v>
-      </c>
+      <c r="L81" s="6" t="n"/>
+      <c r="M81" s="6" t="n"/>
       <c r="N81" s="6" t="n">
         <v>50</v>
       </c>
@@ -5309,25 +5967,31 @@
         <v>50</v>
       </c>
       <c r="Q81" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S81" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R81" s="6" t="n">
+      <c r="T81" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S81" s="6" t="n">
+      <c r="U81" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="T81" s="6" t="inlineStr">
+      <c r="V81" s="6" t="inlineStr">
         <is>
           <t>80.00%</t>
         </is>
       </c>
-      <c r="U81" s="8" t="inlineStr">
+      <c r="W81" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V81" s="9" t="inlineStr">
+      <c r="X81" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5344,14 +6008,18 @@
           <t>Gaurav Kumar</t>
         </is>
       </c>
-      <c r="C82" s="10" t="n">
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Pankaj Rawat</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>28-Dec-2012</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="n">
         <v>12</v>
-      </c>
-      <c r="D82" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>30</v>
       </c>
       <c r="F82" s="10" t="n">
         <v>50</v>
@@ -5363,45 +6031,51 @@
         <v>50</v>
       </c>
       <c r="I82" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K82" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M82" s="10" t="n">
+      <c r="L82" s="10" t="n"/>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O82" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="N82" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O82" s="10" t="n">
+      <c r="P82" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q82" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="P82" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q82" s="10" t="n">
+      <c r="R82" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S82" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="R82" s="10" t="n">
+      <c r="T82" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S82" s="10" t="n">
+      <c r="U82" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="T82" s="10" t="inlineStr">
+      <c r="V82" s="10" t="inlineStr">
         <is>
           <t>61.67%</t>
         </is>
       </c>
-      <c r="U82" s="13" t="inlineStr">
+      <c r="W82" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V82" s="12" t="inlineStr">
+      <c r="X82" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5418,64 +6092,74 @@
           <t>Mohit Kumar</t>
         </is>
       </c>
-      <c r="C83" s="6" t="n">
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Dharmendra Rawat</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>19-Oct-2014</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E83" s="6" t="n">
+      <c r="F83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G83" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="F83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G83" s="6" t="n">
+      <c r="H83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I83" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="H83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I83" s="6" t="n">
+      <c r="J83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K83" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="6" t="n"/>
-      <c r="L83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M83" s="6" t="n">
+      <c r="L83" s="6" t="n"/>
+      <c r="M83" s="6" t="n"/>
+      <c r="N83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O83" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="N83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O83" s="6" t="n">
+      <c r="P83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q83" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="P83" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q83" s="6" t="n">
+      <c r="R83" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S83" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="R83" s="6" t="n">
+      <c r="T83" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S83" s="6" t="n">
+      <c r="U83" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="T83" s="6" t="inlineStr">
+      <c r="V83" s="6" t="inlineStr">
         <is>
           <t>80.00%</t>
         </is>
       </c>
-      <c r="U83" s="8" t="inlineStr">
+      <c r="W83" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V83" s="9" t="inlineStr">
+      <c r="X83" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5492,35 +6176,39 @@
           <t>Mousam Kumari</t>
         </is>
       </c>
-      <c r="C84" s="10" t="n">
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Vijay Rawat</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>14-Mar-2013</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D84" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E84" s="10" t="n">
+      <c r="F84" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G84" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="F84" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G84" s="10" t="n">
+      <c r="H84" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I84" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="H84" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I84" s="10" t="n">
+      <c r="J84" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K84" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="J84" s="10" t="n"/>
-      <c r="K84" s="10" t="n"/>
-      <c r="L84" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M84" s="10" t="n">
-        <v>45</v>
-      </c>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
       <c r="N84" s="10" t="n">
         <v>50</v>
       </c>
@@ -5531,25 +6219,31 @@
         <v>50</v>
       </c>
       <c r="Q84" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="R84" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S84" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="R84" s="10" t="n">
+      <c r="T84" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S84" s="10" t="n">
+      <c r="U84" s="10" t="n">
         <v>263</v>
       </c>
-      <c r="T84" s="10" t="inlineStr">
+      <c r="V84" s="10" t="inlineStr">
         <is>
           <t>87.67%</t>
         </is>
       </c>
-      <c r="U84" s="12" t="inlineStr">
+      <c r="W84" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V84" s="12" t="inlineStr">
+      <c r="X84" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5566,20 +6260,24 @@
           <t>Suraj Kumar</t>
         </is>
       </c>
-      <c r="C85" s="6" t="n">
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Ravindar Kumar Tiwari</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>05-May-2013</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="D85" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E85" s="6" t="n">
+      <c r="F85" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G85" s="6" t="n">
         <v>24</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G85" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="H85" s="6" t="n">
         <v>50</v>
@@ -5587,43 +6285,49 @@
       <c r="I85" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
-      <c r="L85" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M85" s="6" t="n">
+      <c r="J85" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K85" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L85" s="6" t="n"/>
+      <c r="M85" s="6" t="n"/>
       <c r="N85" s="6" t="n">
         <v>50</v>
       </c>
       <c r="O85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q85" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="P85" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q85" s="6" t="n">
+      <c r="R85" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S85" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R85" s="6" t="n">
+      <c r="T85" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S85" s="6" t="n">
+      <c r="U85" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="T85" s="6" t="inlineStr">
+      <c r="V85" s="6" t="inlineStr">
         <is>
           <t>19.67%</t>
         </is>
       </c>
-      <c r="U85" s="17" t="inlineStr">
+      <c r="W85" s="17" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="V85" s="17" t="inlineStr">
+      <c r="X85" s="17" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -5652,6 +6356,8 @@
       <c r="T86" s="16" t="n"/>
       <c r="U86" s="16" t="n"/>
       <c r="V86" s="16" t="n"/>
+      <c r="W86" s="16" t="n"/>
+      <c r="X86" s="16" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -5671,64 +6377,74 @@
           <t>Aarohi Singh</t>
         </is>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Nandan Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>08-Feb-2012</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D88" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E88" s="6" t="n">
+      <c r="F88" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G88" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F88" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G88" s="6" t="n">
-        <v>50</v>
-      </c>
       <c r="H88" s="6" t="n">
         <v>50</v>
       </c>
       <c r="I88" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K88" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="6" t="n"/>
-      <c r="L88" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M88" s="6" t="n">
+      <c r="L88" s="6" t="n"/>
+      <c r="M88" s="6" t="n"/>
+      <c r="N88" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O88" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="N88" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O88" s="6" t="n">
+      <c r="P88" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q88" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="P88" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q88" s="6" t="n">
+      <c r="R88" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S88" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="R88" s="6" t="n">
+      <c r="T88" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S88" s="6" t="n">
+      <c r="U88" s="6" t="n">
         <v>286</v>
       </c>
-      <c r="T88" s="6" t="inlineStr">
+      <c r="V88" s="6" t="inlineStr">
         <is>
           <t>95.33%</t>
         </is>
       </c>
-      <c r="U88" s="9" t="inlineStr">
+      <c r="W88" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V88" s="9" t="inlineStr">
+      <c r="X88" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5745,64 +6461,74 @@
           <t>Manasi Kumari</t>
         </is>
       </c>
-      <c r="C89" s="10" t="n">
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Praveen Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>01-Jan-2011</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E89" s="10" t="n">
+      <c r="F89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G89" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="F89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G89" s="10" t="n">
+      <c r="H89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I89" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="H89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I89" s="10" t="n">
+      <c r="J89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K89" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="J89" s="10" t="n"/>
-      <c r="K89" s="10" t="n"/>
-      <c r="L89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M89" s="10" t="n">
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O89" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="N89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O89" s="10" t="n">
+      <c r="P89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q89" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="P89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q89" s="10" t="n">
+      <c r="R89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S89" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="R89" s="10" t="n">
+      <c r="T89" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S89" s="10" t="n">
+      <c r="U89" s="10" t="n">
         <v>285</v>
       </c>
-      <c r="T89" s="10" t="inlineStr">
+      <c r="V89" s="10" t="inlineStr">
         <is>
           <t>95.00%</t>
         </is>
       </c>
-      <c r="U89" s="12" t="inlineStr">
+      <c r="W89" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V89" s="12" t="inlineStr">
+      <c r="X89" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5819,40 +6545,44 @@
           <t>Ritu Kumari</t>
         </is>
       </c>
-      <c r="C90" s="6" t="n">
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Jitendra Rawat</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>16-Jun-2011</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D90" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E90" s="6" t="n">
+      <c r="F90" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G90" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="F90" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G90" s="6" t="n">
+      <c r="H90" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I90" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="H90" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I90" s="6" t="n">
+      <c r="J90" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K90" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="6" t="n"/>
-      <c r="L90" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M90" s="6" t="n">
+      <c r="L90" s="6" t="n"/>
+      <c r="M90" s="6" t="n"/>
+      <c r="N90" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O90" s="6" t="n">
         <v>48</v>
-      </c>
-      <c r="N90" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O90" s="6" t="n">
-        <v>45</v>
       </c>
       <c r="P90" s="6" t="n">
         <v>50</v>
@@ -5861,22 +6591,28 @@
         <v>45</v>
       </c>
       <c r="R90" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S90" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="T90" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S90" s="6" t="n">
+      <c r="U90" s="6" t="n">
         <v>268</v>
       </c>
-      <c r="T90" s="6" t="inlineStr">
+      <c r="V90" s="6" t="inlineStr">
         <is>
           <t>89.33%</t>
         </is>
       </c>
-      <c r="U90" s="9" t="inlineStr">
+      <c r="W90" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V90" s="9" t="inlineStr">
+      <c r="X90" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5893,35 +6629,39 @@
           <t>Sapna Kumari</t>
         </is>
       </c>
-      <c r="C91" s="10" t="n">
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Etawari Tanti</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>03-Jan-2013</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D91" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E91" s="10" t="n">
+      <c r="F91" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="F91" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G91" s="10" t="n">
+      <c r="H91" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I91" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="H91" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I91" s="10" t="n">
+      <c r="J91" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K91" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M91" s="10" t="n">
-        <v>46</v>
-      </c>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
       <c r="N91" s="10" t="n">
         <v>50</v>
       </c>
@@ -5932,25 +6672,31 @@
         <v>50</v>
       </c>
       <c r="Q91" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="R91" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S91" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="R91" s="10" t="n">
+      <c r="T91" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S91" s="10" t="n">
+      <c r="U91" s="10" t="n">
         <v>261</v>
       </c>
-      <c r="T91" s="10" t="inlineStr">
+      <c r="V91" s="10" t="inlineStr">
         <is>
           <t>87.00%</t>
         </is>
       </c>
-      <c r="U91" s="12" t="inlineStr">
+      <c r="W91" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V91" s="12" t="inlineStr">
+      <c r="X91" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5967,40 +6713,44 @@
           <t>Varsha Kumari</t>
         </is>
       </c>
-      <c r="C92" s="6" t="n">
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Vijay Rawat</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>06-Jan-2012</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D92" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E92" s="6" t="n">
+      <c r="F92" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G92" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="F92" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G92" s="6" t="n">
+      <c r="H92" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I92" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="H92" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I92" s="6" t="n">
+      <c r="J92" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K92" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="6" t="n"/>
-      <c r="L92" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M92" s="6" t="n">
+      <c r="L92" s="6" t="n"/>
+      <c r="M92" s="6" t="n"/>
+      <c r="N92" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O92" s="6" t="n">
         <v>49</v>
-      </c>
-      <c r="N92" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O92" s="6" t="n">
-        <v>48</v>
       </c>
       <c r="P92" s="6" t="n">
         <v>50</v>
@@ -6009,22 +6759,28 @@
         <v>48</v>
       </c>
       <c r="R92" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S92" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="T92" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S92" s="6" t="n">
+      <c r="U92" s="6" t="n">
         <v>276</v>
       </c>
-      <c r="T92" s="6" t="inlineStr">
+      <c r="V92" s="6" t="inlineStr">
         <is>
           <t>92.00%</t>
         </is>
       </c>
-      <c r="U92" s="9" t="inlineStr">
+      <c r="W92" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V92" s="9" t="inlineStr">
+      <c r="X92" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6041,40 +6797,44 @@
           <t>Adity Gaurav</t>
         </is>
       </c>
-      <c r="C93" s="10" t="n">
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Manish Tiwari</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>31-Jul-2013</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D93" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E93" s="10" t="n">
+      <c r="F93" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G93" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="F93" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G93" s="10" t="n">
+      <c r="H93" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I93" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="H93" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I93" s="10" t="n">
+      <c r="J93" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K93" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M93" s="10" t="n">
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O93" s="10" t="n">
         <v>48</v>
-      </c>
-      <c r="N93" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O93" s="10" t="n">
-        <v>42</v>
       </c>
       <c r="P93" s="10" t="n">
         <v>50</v>
@@ -6083,22 +6843,28 @@
         <v>42</v>
       </c>
       <c r="R93" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S93" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="T93" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S93" s="10" t="n">
+      <c r="U93" s="10" t="n">
         <v>270</v>
       </c>
-      <c r="T93" s="10" t="inlineStr">
+      <c r="V93" s="10" t="inlineStr">
         <is>
           <t>90.00%</t>
         </is>
       </c>
-      <c r="U93" s="12" t="inlineStr">
+      <c r="W93" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V93" s="12" t="inlineStr">
+      <c r="X93" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6115,64 +6881,74 @@
           <t>Abhishek Kumar</t>
         </is>
       </c>
-      <c r="C94" s="6" t="n">
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Krishna Tanti</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>01-Jan-2012</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D94" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E94" s="6" t="n">
+      <c r="F94" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G94" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F94" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G94" s="6" t="n">
+      <c r="H94" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I94" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H94" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I94" s="6" t="n">
+      <c r="J94" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K94" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="6" t="n"/>
-      <c r="L94" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M94" s="6" t="n">
+      <c r="L94" s="6" t="n"/>
+      <c r="M94" s="6" t="n"/>
+      <c r="N94" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O94" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="N94" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O94" s="6" t="n">
+      <c r="P94" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q94" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="P94" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q94" s="6" t="n">
+      <c r="R94" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S94" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R94" s="6" t="n">
+      <c r="T94" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S94" s="6" t="n">
+      <c r="U94" s="6" t="n">
         <v>259</v>
       </c>
-      <c r="T94" s="6" t="inlineStr">
+      <c r="V94" s="6" t="inlineStr">
         <is>
           <t>86.33%</t>
         </is>
       </c>
-      <c r="U94" s="9" t="inlineStr">
+      <c r="W94" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V94" s="9" t="inlineStr">
+      <c r="X94" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6189,64 +6965,74 @@
           <t>Ritu Kumari</t>
         </is>
       </c>
-      <c r="C95" s="10" t="n">
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Ramchandar Rawat</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>10-Aug-2012</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D95" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E95" s="10" t="n">
+      <c r="F95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G95" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F95" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G95" s="10" t="n">
+      <c r="H95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I95" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="H95" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I95" s="10" t="n">
+      <c r="J95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K95" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="J95" s="10" t="n"/>
-      <c r="K95" s="10" t="n"/>
-      <c r="L95" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M95" s="10" t="n">
+      <c r="L95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O95" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="N95" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O95" s="10" t="n">
+      <c r="P95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q95" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="P95" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q95" s="10" t="n">
+      <c r="R95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S95" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R95" s="10" t="n">
+      <c r="T95" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S95" s="10" t="n">
+      <c r="U95" s="10" t="n">
         <v>262</v>
       </c>
-      <c r="T95" s="10" t="inlineStr">
+      <c r="V95" s="10" t="inlineStr">
         <is>
           <t>87.33%</t>
         </is>
       </c>
-      <c r="U95" s="12" t="inlineStr">
+      <c r="W95" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V95" s="12" t="inlineStr">
+      <c r="X95" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6263,64 +7049,74 @@
           <t>Shivani Kumari</t>
         </is>
       </c>
-      <c r="C96" s="6" t="n">
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Ramchandra Tanti</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>01-Jan-2012</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D96" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E96" s="6" t="n">
+      <c r="F96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G96" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="F96" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G96" s="6" t="n">
+      <c r="H96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I96" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H96" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I96" s="6" t="n">
+      <c r="J96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K96" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="6" t="n"/>
-      <c r="L96" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M96" s="6" t="n">
+      <c r="L96" s="6" t="n"/>
+      <c r="M96" s="6" t="n"/>
+      <c r="N96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O96" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="N96" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O96" s="6" t="n">
+      <c r="P96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q96" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="P96" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q96" s="6" t="n">
+      <c r="R96" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S96" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="R96" s="6" t="n">
+      <c r="T96" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S96" s="6" t="n">
+      <c r="U96" s="6" t="n">
         <v>234</v>
       </c>
-      <c r="T96" s="6" t="inlineStr">
+      <c r="V96" s="6" t="inlineStr">
         <is>
           <t>78.00%</t>
         </is>
       </c>
-      <c r="U96" s="8" t="inlineStr">
+      <c r="W96" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V96" s="9" t="inlineStr">
+      <c r="X96" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6337,64 +7133,74 @@
           <t>Subham Raj</t>
         </is>
       </c>
-      <c r="C97" s="10" t="n">
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Dilip Ravidas</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>30-Sep-2012</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D97" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E97" s="10" t="n">
+      <c r="F97" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G97" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F97" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G97" s="10" t="n">
+      <c r="H97" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I97" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="H97" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I97" s="10" t="n">
+      <c r="J97" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K97" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M97" s="10" t="n">
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O97" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="N97" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O97" s="10" t="n">
+      <c r="P97" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q97" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="P97" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q97" s="10" t="n">
+      <c r="R97" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S97" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="R97" s="10" t="n">
+      <c r="T97" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S97" s="10" t="n">
+      <c r="U97" s="10" t="n">
         <v>260</v>
       </c>
-      <c r="T97" s="10" t="inlineStr">
+      <c r="V97" s="10" t="inlineStr">
         <is>
           <t>86.67%</t>
         </is>
       </c>
-      <c r="U97" s="12" t="inlineStr">
+      <c r="W97" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V97" s="12" t="inlineStr">
+      <c r="X97" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6411,64 +7217,74 @@
           <t>Abhishek Kumar</t>
         </is>
       </c>
-      <c r="C98" s="6" t="n">
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Sunil Rawat</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>13-Aug-2011</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D98" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E98" s="6" t="n">
+      <c r="F98" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G98" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F98" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G98" s="6" t="n">
+      <c r="H98" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I98" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="H98" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I98" s="6" t="n">
+      <c r="J98" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K98" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="J98" s="6" t="n"/>
-      <c r="K98" s="6" t="n"/>
-      <c r="L98" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M98" s="6" t="n">
+      <c r="L98" s="6" t="n"/>
+      <c r="M98" s="6" t="n"/>
+      <c r="N98" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O98" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="N98" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O98" s="6" t="n">
+      <c r="P98" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q98" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="P98" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q98" s="6" t="n">
+      <c r="R98" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S98" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="R98" s="6" t="n">
+      <c r="T98" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S98" s="6" t="n">
+      <c r="U98" s="6" t="n">
         <v>261</v>
       </c>
-      <c r="T98" s="6" t="inlineStr">
+      <c r="V98" s="6" t="inlineStr">
         <is>
           <t>87.00%</t>
         </is>
       </c>
-      <c r="U98" s="9" t="inlineStr">
+      <c r="W98" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V98" s="9" t="inlineStr">
+      <c r="X98" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6485,64 +7301,74 @@
           <t>Shivani Kumari</t>
         </is>
       </c>
-      <c r="C99" s="10" t="n">
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Mukesh Rawat</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>04-Aug-2012</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D99" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E99" s="10" t="n">
+      <c r="F99" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G99" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="F99" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G99" s="10" t="n">
+      <c r="H99" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I99" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="H99" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I99" s="10" t="n">
+      <c r="J99" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K99" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M99" s="10" t="n">
+      <c r="L99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O99" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="N99" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O99" s="10" t="n">
+      <c r="P99" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q99" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="P99" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q99" s="10" t="n">
+      <c r="R99" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S99" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="R99" s="10" t="n">
+      <c r="T99" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S99" s="10" t="n">
+      <c r="U99" s="10" t="n">
         <v>258</v>
       </c>
-      <c r="T99" s="10" t="inlineStr">
+      <c r="V99" s="10" t="inlineStr">
         <is>
           <t>86.00%</t>
         </is>
       </c>
-      <c r="U99" s="12" t="inlineStr">
+      <c r="W99" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V99" s="12" t="inlineStr">
+      <c r="X99" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6559,64 +7385,74 @@
           <t>Laxami Kumari</t>
         </is>
       </c>
-      <c r="C100" s="6" t="n">
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Manu Rawat</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>27-Oct-2011</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D100" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E100" s="6" t="n">
+      <c r="F100" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G100" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F100" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G100" s="6" t="n">
+      <c r="H100" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I100" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="H100" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I100" s="6" t="n">
+      <c r="J100" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K100" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="6" t="n"/>
-      <c r="L100" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M100" s="6" t="n">
+      <c r="L100" s="6" t="n"/>
+      <c r="M100" s="6" t="n"/>
+      <c r="N100" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O100" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="N100" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O100" s="6" t="n">
+      <c r="P100" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q100" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="P100" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q100" s="6" t="n">
+      <c r="R100" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S100" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="R100" s="6" t="n">
+      <c r="T100" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S100" s="6" t="n">
+      <c r="U100" s="6" t="n">
         <v>211</v>
       </c>
-      <c r="T100" s="6" t="inlineStr">
+      <c r="V100" s="6" t="inlineStr">
         <is>
           <t>70.33%</t>
         </is>
       </c>
-      <c r="U100" s="8" t="inlineStr">
+      <c r="W100" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V100" s="9" t="inlineStr">
+      <c r="X100" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6633,40 +7469,44 @@
           <t>Ritesh Kumar</t>
         </is>
       </c>
-      <c r="C101" s="10" t="n">
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Bajrangi Rawat</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>05-Apr-2013</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D101" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E101" s="10" t="n">
+      <c r="F101" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G101" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="F101" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G101" s="10" t="n">
+      <c r="H101" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I101" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="H101" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I101" s="10" t="n">
+      <c r="J101" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K101" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M101" s="10" t="n">
+      <c r="L101" s="10" t="n"/>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O101" s="10" t="n">
         <v>46</v>
-      </c>
-      <c r="N101" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O101" s="10" t="n">
-        <v>40</v>
       </c>
       <c r="P101" s="10" t="n">
         <v>50</v>
@@ -6675,22 +7515,28 @@
         <v>40</v>
       </c>
       <c r="R101" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="S101" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="T101" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="S101" s="10" t="n">
+      <c r="U101" s="10" t="n">
         <v>255</v>
       </c>
-      <c r="T101" s="10" t="inlineStr">
+      <c r="V101" s="10" t="inlineStr">
         <is>
           <t>85.00%</t>
         </is>
       </c>
-      <c r="U101" s="12" t="inlineStr">
+      <c r="W101" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V101" s="12" t="inlineStr">
+      <c r="X101" s="12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6707,64 +7553,74 @@
           <t>Abhijit Kumar</t>
         </is>
       </c>
-      <c r="C102" s="6" t="n">
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Manohar Das</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>15-May-2013</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="D102" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E102" s="6" t="n">
+      <c r="F102" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G102" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="F102" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G102" s="6" t="n">
+      <c r="H102" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I102" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="H102" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I102" s="6" t="n">
+      <c r="J102" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K102" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="J102" s="6" t="n"/>
-      <c r="K102" s="6" t="n"/>
-      <c r="L102" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M102" s="6" t="n">
+      <c r="L102" s="6" t="n"/>
+      <c r="M102" s="6" t="n"/>
+      <c r="N102" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O102" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="N102" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="O102" s="6" t="n">
+      <c r="P102" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q102" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="P102" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q102" s="6" t="n">
+      <c r="R102" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S102" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="R102" s="6" t="n">
+      <c r="T102" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="S102" s="6" t="n">
+      <c r="U102" s="6" t="n">
         <v>235</v>
       </c>
-      <c r="T102" s="6" t="inlineStr">
+      <c r="V102" s="6" t="inlineStr">
         <is>
           <t>78.33%</t>
         </is>
       </c>
-      <c r="U102" s="8" t="inlineStr">
+      <c r="W102" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V102" s="9" t="inlineStr">
+      <c r="X102" s="9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6772,17 +7628,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A51:V51"/>
-    <mergeCell ref="A41:V41"/>
-    <mergeCell ref="A5:V5"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A14:V14"/>
-    <mergeCell ref="A22:V22"/>
-    <mergeCell ref="A87:V87"/>
-    <mergeCell ref="A70:V70"/>
-    <mergeCell ref="A3:V3"/>
-    <mergeCell ref="A29:V29"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A87:X87"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="A51:X51"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A14:X14"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="A70:X70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
